--- a/public/paper-sample-tree-ledger.xlsx
+++ b/public/paper-sample-tree-ledger.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="102">
   <si>
     <t>{{발행처로고}}</t>
   </si>
@@ -24,223 +24,217 @@
     <t>내 역 서</t>
   </si>
   <si>
+    <t>▼ 이 행의 역할</t>
+  </si>
+  <si>
+    <t>현 장 명</t>
+  </si>
+  <si>
+    <t>{{현장명}}</t>
+  </si>
+  <si>
+    <t>{{번호:품목.품명}}</t>
+  </si>
+  <si>
+    <t>그룹머리</t>
+  </si>
+  <si>
+    <t>공　사</t>
+  </si>
+  <si>
+    <t>단위</t>
+  </si>
+  <si>
+    <t>수량</t>
+  </si>
+  <si>
+    <t>단가</t>
+  </si>
+  <si>
+    <t>금액</t>
+  </si>
+  <si>
+    <t>비고</t>
+  </si>
+  <si>
+    <t>열머리</t>
+  </si>
+  <si>
+    <t>{{들여:품목.품명}}</t>
+  </si>
+  <si>
+    <t>{{품목.단위}}</t>
+  </si>
+  <si>
+    <t>{{품목.수량}}</t>
+  </si>
+  <si>
+    <t>{{품목.단가}}</t>
+  </si>
+  <si>
+    <t>{{품목.금액}}</t>
+  </si>
+  <si>
+    <t>{{품목.비고}}</t>
+  </si>
+  <si>
+    <t>반복</t>
+  </si>
+  <si>
+    <t>소　계</t>
+  </si>
+  <si>
+    <t>{{합계:품목.금액}}</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>그룹꼬리</t>
+  </si>
+  <si>
+    <t>총　계</t>
+  </si>
+  <si>
+    <t>합계</t>
+  </si>
+  <si>
+    <t>{{발행처명}}　{{발행처주소}}　{{발행처전화}}</t>
+  </si>
+  <si>
+    <t>{{@쪽}} / {{@총쪽}}</t>
+  </si>
+  <si>
+    <t>꼬리말</t>
+  </si>
+  <si>
+    <t>이름</t>
+  </si>
+  <si>
+    <t>라벨</t>
+  </si>
+  <si>
+    <t>종류</t>
+  </si>
+  <si>
+    <t>필수</t>
+  </si>
+  <si>
+    <t>배열</t>
+  </si>
+  <si>
+    <t>── 표준(모든 문서 공통) ──</t>
+  </si>
+  <si>
+    <t>발행처로고</t>
+  </si>
+  <si>
+    <t>발행처 로고</t>
+  </si>
+  <si>
+    <t>이미지</t>
+  </si>
+  <si>
+    <t>발행처명</t>
+  </si>
+  <si>
+    <t>발행처 이름</t>
+  </si>
+  <si>
+    <t>글자</t>
+  </si>
+  <si>
+    <t>발행처사업자번호</t>
+  </si>
+  <si>
+    <t>발행처 사업자번호</t>
+  </si>
+  <si>
+    <t>발행처주소</t>
+  </si>
+  <si>
+    <t>발행처 주소</t>
+  </si>
+  <si>
+    <t>발행처전화</t>
+  </si>
+  <si>
+    <t>발행처 전화</t>
+  </si>
+  <si>
     <t>문서번호</t>
   </si>
   <si>
+    <t>작성일자</t>
+  </si>
+  <si>
+    <t>날짜</t>
+  </si>
+  <si>
+    <t>담당자</t>
+  </si>
+  <si>
+    <t>검토자</t>
+  </si>
+  <si>
+    <t>승인자</t>
+  </si>
+  <si>
+    <t>── 이 문서 전용 ──</t>
+  </si>
+  <si>
+    <t>현장명</t>
+  </si>
+  <si>
+    <t>레벨</t>
+  </si>
+  <si>
+    <t>깊이</t>
+  </si>
+  <si>
+    <t>품목</t>
+  </si>
+  <si>
+    <t>품명</t>
+  </si>
+  <si>
+    <t>숫자</t>
+  </si>
+  <si>
+    <t>시작하는 법</t>
+  </si>
+  <si>
+    <t>「양식」 시트의 24열 × 42행이 A4 한 쪽입니다. 표준 머리(1~7행)와 꼬리(42행)는 이미 놓여 있으니 8행부터 채우면 됩니다.</t>
+  </si>
+  <si>
+    <t>칸을 병합하고 테두리를 그려서 문서를 만듭니다. 회색 글씨는 값이 들어갈 자리 표시입니다.</t>
+  </si>
+  <si>
+    <t>건드리지 말 것</t>
+  </si>
+  <si>
+    <t>열 너비</t>
+  </si>
+  <si>
+    <t>넓은 칸이 필요하면 옆 칸과 «병합»합니다. 열 너비를 바꾸면 24열 격자가 깨집니다.</t>
+  </si>
+  <si>
+    <t>행 높이</t>
+  </si>
+  <si>
+    <t>기본 18pt(=한 칸). 높은 칸은 36pt·54pt처럼 18의 배수로 둡니다.</t>
+  </si>
+  <si>
+    <t>세로 정렬</t>
+  </si>
+  <si>
+    <t>엑셀은 세로 정렬을 안 정하면 «아래»에 붙여 그리지만, 인쇄물은 «가운데»로 나갑니다. 엑셀 화면과 결과를 맞추려면 세로 정렬을 «가운데»로 지정해 두세요(결과가 바뀌지는 않습니다).</t>
+  </si>
+  <si>
+    <t>값이 들어갈 자리</t>
+  </si>
+  <si>
     <t>{{문서번호}}</t>
-  </si>
-  <si>
-    <t>▼ 이 행의 역할</t>
-  </si>
-  <si>
-    <t>작성일자</t>
-  </si>
-  <si>
-    <t>{{작성일자}}</t>
-  </si>
-  <si>
-    <t>현 장 명</t>
-  </si>
-  <si>
-    <t>{{현장명}}</t>
-  </si>
-  <si>
-    <t>고 객 명</t>
-  </si>
-  <si>
-    <t>{{고객명}}</t>
-  </si>
-  <si>
-    <t>{{번호:품목.품명}}</t>
-  </si>
-  <si>
-    <t>그룹머리</t>
-  </si>
-  <si>
-    <t>공　사</t>
-  </si>
-  <si>
-    <t>단위</t>
-  </si>
-  <si>
-    <t>수량</t>
-  </si>
-  <si>
-    <t>단가</t>
-  </si>
-  <si>
-    <t>금액</t>
-  </si>
-  <si>
-    <t>비고</t>
-  </si>
-  <si>
-    <t>열머리</t>
-  </si>
-  <si>
-    <t>{{들여:품목.품명}}</t>
-  </si>
-  <si>
-    <t>{{품목.단위}}</t>
-  </si>
-  <si>
-    <t>{{품목.수량}}</t>
-  </si>
-  <si>
-    <t>{{품목.단가}}</t>
-  </si>
-  <si>
-    <t>{{품목.금액}}</t>
-  </si>
-  <si>
-    <t>{{품목.비고}}</t>
-  </si>
-  <si>
-    <t>반복</t>
-  </si>
-  <si>
-    <t>소　계</t>
-  </si>
-  <si>
-    <t>{{합계:품목.금액}}</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>그룹꼬리</t>
-  </si>
-  <si>
-    <t>총　계</t>
-  </si>
-  <si>
-    <t>합계</t>
-  </si>
-  <si>
-    <t>{{발행처명}}　{{발행처주소}}　{{발행처전화}}</t>
-  </si>
-  <si>
-    <t>{{@쪽}} / {{@총쪽}}</t>
-  </si>
-  <si>
-    <t>꼬리말</t>
-  </si>
-  <si>
-    <t>이름</t>
-  </si>
-  <si>
-    <t>라벨</t>
-  </si>
-  <si>
-    <t>종류</t>
-  </si>
-  <si>
-    <t>필수</t>
-  </si>
-  <si>
-    <t>배열</t>
-  </si>
-  <si>
-    <t>── 표준(모든 문서 공통) ──</t>
-  </si>
-  <si>
-    <t>발행처로고</t>
-  </si>
-  <si>
-    <t>발행처 로고</t>
-  </si>
-  <si>
-    <t>이미지</t>
-  </si>
-  <si>
-    <t>발행처명</t>
-  </si>
-  <si>
-    <t>발행처 이름</t>
-  </si>
-  <si>
-    <t>글자</t>
-  </si>
-  <si>
-    <t>발행처사업자번호</t>
-  </si>
-  <si>
-    <t>발행처 사업자번호</t>
-  </si>
-  <si>
-    <t>발행처주소</t>
-  </si>
-  <si>
-    <t>발행처 주소</t>
-  </si>
-  <si>
-    <t>발행처전화</t>
-  </si>
-  <si>
-    <t>발행처 전화</t>
-  </si>
-  <si>
-    <t>날짜</t>
-  </si>
-  <si>
-    <t>담당자</t>
-  </si>
-  <si>
-    <t>검토자</t>
-  </si>
-  <si>
-    <t>승인자</t>
-  </si>
-  <si>
-    <t>── 이 문서 전용 ──</t>
-  </si>
-  <si>
-    <t>현장명</t>
-  </si>
-  <si>
-    <t>고객명</t>
-  </si>
-  <si>
-    <t>레벨</t>
-  </si>
-  <si>
-    <t>깊이</t>
-  </si>
-  <si>
-    <t>품목</t>
-  </si>
-  <si>
-    <t>품명</t>
-  </si>
-  <si>
-    <t>숫자</t>
-  </si>
-  <si>
-    <t>시작하는 법</t>
-  </si>
-  <si>
-    <t>「양식」 시트의 24열 × 42행이 A4 한 쪽입니다. 표준 머리(1~7행)와 꼬리(42행)는 이미 놓여 있으니 8행부터 채우면 됩니다.</t>
-  </si>
-  <si>
-    <t>칸을 병합하고 테두리를 그려서 문서를 만듭니다. 회색 글씨는 값이 들어갈 자리 표시입니다.</t>
-  </si>
-  <si>
-    <t>건드리지 말 것</t>
-  </si>
-  <si>
-    <t>열 너비</t>
-  </si>
-  <si>
-    <t>넓은 칸이 필요하면 옆 칸과 «병합»합니다. 열 너비를 바꾸면 24열 격자가 깨집니다.</t>
-  </si>
-  <si>
-    <t>행 높이</t>
-  </si>
-  <si>
-    <t>기본 18pt(=한 칸). 높은 칸은 36pt·54pt처럼 18의 배수로 둡니다.</t>
-  </si>
-  <si>
-    <t>값이 들어갈 자리</t>
   </si>
   <si>
     <t>「필드」 시트에 적은 이름을 두 겹 중괄호로 씁니다.</t>
@@ -354,11 +348,6 @@
       <name val="맑은 고딕"/>
     </font>
     <font>
-      <color rgb="FF16181C"/>
-      <sz val="8"/>
-      <name val="맑은 고딕"/>
-    </font>
-    <font>
       <b/>
       <color rgb="FF9CA1AD"/>
       <sz val="9"/>
@@ -379,6 +368,12 @@
       <sz val="9"/>
     </font>
     <font>
+      <b/>
+      <color rgb="FF16181C"/>
+      <sz val="12"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
       <color rgb="FF9CA1AD"/>
       <sz val="8"/>
       <name val="맑은 고딕"/>
@@ -397,7 +392,7 @@
       <name val="맑은 고딕"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -409,8 +404,13 @@
         <fgColor rgb="FFE4E4E4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0D0D0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -434,6 +434,126 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color rgb="FF16181C"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF16181C"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF16181C"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF6E7480"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF16181C"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF6E7480"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF6E7480"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF6E7480"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF6E7480"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF16181C"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF6E7480"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF6E7480"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF16181C"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF6E7480"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF6E7480"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF16181C"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF6E7480"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF6E7480"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF6E7480"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF16181C"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF6E7480"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF16181C"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF6E7480"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF16181C"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF16181C"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF6E7480"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF16181C"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF16181C"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF6E7480"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF16181C"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF16181C"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF16181C"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -446,7 +566,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -454,45 +574,57 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -870,19 +1002,12 @@
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="Z1" s="3" t="s">
         <v>2</v>
-      </c>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="V1" s="4"/>
-      <c r="W1" s="4"/>
-      <c r="X1" s="4"/>
-      <c r="Z1" s="5" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
@@ -903,238 +1028,253 @@
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
-      <c r="R2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="U2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="7"/>
-      <c r="V3" s="7"/>
-      <c r="W3" s="7"/>
-      <c r="X3" s="7"/>
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
+      <c r="U3" s="5"/>
+      <c r="V3" s="5"/>
+      <c r="W3" s="5"/>
+      <c r="X3" s="5"/>
     </row>
     <row r="4" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
     <row r="5" ht="18" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="6"/>
+      <c r="T5" s="6"/>
+      <c r="U5" s="6"/>
+      <c r="V5" s="6"/>
+      <c r="W5" s="6"/>
+      <c r="X5" s="6"/>
+      <c r="Z5" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="8"/>
-      <c r="R5" s="8"/>
-      <c r="S5" s="8"/>
-      <c r="T5" s="8"/>
-      <c r="U5" s="8"/>
-      <c r="V5" s="8"/>
-      <c r="W5" s="8"/>
-      <c r="X5" s="8"/>
-      <c r="Z5" s="9" t="s">
+      <c r="R6" s="9"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="9"/>
+      <c r="U6" s="10" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10"/>
-      <c r="Q6" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="R6" s="10"/>
-      <c r="S6" s="10"/>
-      <c r="T6" s="10"/>
-      <c r="U6" s="10" t="s">
-        <v>18</v>
       </c>
       <c r="V6" s="10"/>
       <c r="W6" s="10"/>
       <c r="X6" s="10"/>
-      <c r="Z6" s="9" t="s">
+      <c r="Z6" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" s="12"/>
+      <c r="K7" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="R7" s="13"/>
+      <c r="S7" s="13"/>
+      <c r="T7" s="13"/>
+      <c r="U7" s="14" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="7" ht="18" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+      <c r="V7" s="14"/>
+      <c r="W7" s="14"/>
+      <c r="X7" s="14"/>
+      <c r="Z7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="11" t="s">
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="J7" s="11"/>
-      <c r="K7" s="12" t="s">
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="15"/>
+      <c r="O8" s="15"/>
+      <c r="P8" s="15"/>
+      <c r="Q8" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="L7" s="12"/>
-      <c r="M7" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="N7" s="12"/>
-      <c r="O7" s="12"/>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="12" t="s">
+      <c r="R8" s="16"/>
+      <c r="S8" s="16"/>
+      <c r="T8" s="16"/>
+      <c r="U8" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="V8" s="17"/>
+      <c r="W8" s="17"/>
+      <c r="X8" s="17"/>
+      <c r="Z8" s="7" t="s">
         <v>24</v>
-      </c>
-      <c r="R7" s="12"/>
-      <c r="S7" s="12"/>
-      <c r="T7" s="12"/>
-      <c r="U7" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="V7" s="7"/>
-      <c r="W7" s="7"/>
-      <c r="X7" s="7"/>
-      <c r="Z7" s="9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="13"/>
-      <c r="Q8" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="R8" s="14"/>
-      <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
-      <c r="U8" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="V8" s="15"/>
-      <c r="W8" s="15"/>
-      <c r="X8" s="15"/>
-      <c r="Z8" s="9" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
     <row r="10" ht="18" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
-      <c r="P10" s="13"/>
-      <c r="Q10" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="R10" s="14"/>
-      <c r="S10" s="14"/>
-      <c r="T10" s="14"/>
-      <c r="U10" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="V10" s="15"/>
-      <c r="W10" s="15"/>
-      <c r="X10" s="15"/>
-      <c r="Z10" s="9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+      <c r="A10" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="18"/>
+      <c r="N10" s="18"/>
+      <c r="O10" s="18"/>
+      <c r="P10" s="18"/>
+      <c r="Q10" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="19"/>
+      <c r="W10" s="19"/>
+      <c r="X10" s="19"/>
+      <c r="Z10" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="18"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="19"/>
+      <c r="W11" s="19"/>
+      <c r="X11" s="19"/>
+      <c r="Z11" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
     <row r="12" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
     <row r="13" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
     <row r="14" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
@@ -1166,50 +1306,44 @@
     <row r="40" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
     <row r="41" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
     <row r="42" ht="18" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A42" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="B42" s="16"/>
-      <c r="C42" s="16"/>
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="16"/>
-      <c r="H42" s="16"/>
-      <c r="I42" s="16"/>
-      <c r="J42" s="16"/>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="16"/>
-      <c r="O42" s="16"/>
-      <c r="P42" s="16"/>
-      <c r="Q42" s="16"/>
-      <c r="R42" s="16"/>
-      <c r="S42" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="T42" s="17"/>
-      <c r="U42" s="17"/>
-      <c r="V42" s="17"/>
-      <c r="W42" s="17"/>
-      <c r="X42" s="17"/>
-      <c r="Z42" s="9" t="s">
-        <v>35</v>
+      <c r="A42" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B42" s="20"/>
+      <c r="C42" s="20"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="20"/>
+      <c r="F42" s="20"/>
+      <c r="G42" s="20"/>
+      <c r="H42" s="20"/>
+      <c r="I42" s="20"/>
+      <c r="J42" s="20"/>
+      <c r="K42" s="20"/>
+      <c r="L42" s="20"/>
+      <c r="M42" s="20"/>
+      <c r="N42" s="20"/>
+      <c r="O42" s="20"/>
+      <c r="P42" s="20"/>
+      <c r="Q42" s="20"/>
+      <c r="R42" s="20"/>
+      <c r="S42" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="T42" s="21"/>
+      <c r="U42" s="21"/>
+      <c r="V42" s="21"/>
+      <c r="W42" s="21"/>
+      <c r="X42" s="21"/>
+      <c r="Z42" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="24">
     <mergeCell ref="A1:C2"/>
-    <mergeCell ref="D1:Q2"/>
-    <mergeCell ref="R1:T1"/>
-    <mergeCell ref="U1:X1"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:X2"/>
+    <mergeCell ref="D1:U2"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:L3"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="P3:X3"/>
+    <mergeCell ref="D3:X3"/>
     <mergeCell ref="A5:X5"/>
     <mergeCell ref="A6:H6"/>
     <mergeCell ref="I6:J6"/>
@@ -1226,9 +1360,8 @@
     <mergeCell ref="A8:P8"/>
     <mergeCell ref="Q8:T8"/>
     <mergeCell ref="U8:X8"/>
-    <mergeCell ref="A10:P10"/>
-    <mergeCell ref="Q10:T10"/>
-    <mergeCell ref="U10:X10"/>
+    <mergeCell ref="A10:P11"/>
+    <mergeCell ref="Q10:X11"/>
     <mergeCell ref="A42:R42"/>
     <mergeCell ref="S42:X42"/>
   </mergeCells>
@@ -1258,360 +1391,344 @@
     <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="E1" s="18" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
+    <row r="1" spans="1:5" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="B8" t="s">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B10" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E14" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B15" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D15" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E15" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B16" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C16" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="D16" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E16" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D17" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="E17" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="D18" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E18" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="D19" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E19" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C20" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D20" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E20" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="D21" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E21" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>18</v>
-      </c>
-      <c r="B22" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22" t="s">
-        <v>47</v>
-      </c>
-      <c r="D22" t="s">
-        <v>29</v>
-      </c>
-      <c r="E22" t="s">
-        <v>63</v>
-      </c>
-    </row>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="3:4" x14ac:dyDescent="0.25"/>
     <row r="23" spans="3:4" x14ac:dyDescent="0.25"/>
     <row r="24" spans="3:4" x14ac:dyDescent="0.25"/>
     <row r="25" spans="3:4" x14ac:dyDescent="0.25"/>
@@ -1692,307 +1809,315 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:2" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+    <row r="1" ht="26" customHeight="1" spans="1:2" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1" spans="1:2" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="19" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1" spans="1:2" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" s="20" t="s">
+    </row>
+    <row r="7" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="24" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="1:2" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="20" t="s">
+      <c r="B7" s="24" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1" spans="1:2" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" ht="26" customHeight="1" spans="1:2" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
+    <row r="8" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="19" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:2" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="20" t="s">
+      <c r="B8" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="20" t="s">
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1" spans="1:2" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="23" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="7" ht="18" customHeight="1" spans="1:2" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="20" t="s">
+      <c r="B10" s="23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B11" s="24" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1" spans="1:2" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" ht="26" customHeight="1" spans="1:2" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+    <row r="12" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="B9" s="19" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1" spans="1:2" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="20" t="s">
+      <c r="B12" s="24" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1" spans="1:2" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="20" t="s">
+    <row r="13" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="B11" s="20" t="s">
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="24" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1" spans="1:2" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="20" t="s">
+    <row r="15" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="24" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1" spans="1:2" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="20" t="s">
+    <row r="16" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="B16" s="24" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1" spans="1:2" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" s="24" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="24" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="24" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="24" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="20" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1" spans="1:2" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1" spans="1:2" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1" spans="1:2" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" ht="26" customHeight="1" spans="1:2" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1" spans="1:2" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1" spans="1:2" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="20" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="1:2" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="B20" s="20" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1" spans="1:2" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="B21" s="20" t="s">
+      <c r="B24" s="24" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1" spans="1:2" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="20" t="s">
+    <row r="25" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="24" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1" spans="1:2" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" s="20" t="s">
+    <row r="26" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1" spans="1:2" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="23" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="24" ht="18" customHeight="1" spans="1:2" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" s="20" t="s">
+      <c r="B27" s="23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" s="24" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1" spans="1:2" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="B25" s="20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="26" ht="26" customHeight="1" spans="1:2" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="19" t="s">
+    <row r="29" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="B26" s="19" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1" spans="1:2" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="B27" s="20" t="s">
+    </row>
+    <row r="30" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B30" s="24" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="28" ht="18" customHeight="1" spans="1:2" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="B28" s="20" t="s">
+    <row r="31" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B31" s="24" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="29" ht="18" customHeight="1" spans="1:2" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" s="20" t="s">
+    <row r="32" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B32" s="24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1" spans="1:2" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="23" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="30" ht="18" customHeight="1" spans="1:2" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="B30" s="20" t="s">
+      <c r="B33" s="23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B34" s="24" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="31" ht="18" customHeight="1" spans="1:2" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="B31" s="20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="32" ht="26" customHeight="1" spans="1:2" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="19" t="s">
+    <row r="35" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B35" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="B32" s="19" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1" spans="1:2" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="B33" s="20" t="s">
+    </row>
+    <row r="36" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B36" s="24" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="34" ht="18" customHeight="1" spans="1:2" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="B34" s="20" t="s">
+    <row r="37" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B37" s="24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="24" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="35" ht="18" customHeight="1" spans="1:2" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="B35" s="20" t="s">
+      <c r="B38" s="24" t="s">
         <v>101</v>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1" spans="1:2" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="B36" s="20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1" spans="1:2" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="B37" s="20" t="s">
-        <v>103</v>
       </c>
     </row>
   </sheetData>
